--- a/Supplementary Information/S4 scRNA Libraries.xlsx
+++ b/Supplementary Information/S4 scRNA Libraries.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\devin\Desktop\paper\claude\metadata\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\devin\Desktop\rrms\Supplementary Information\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{66E8B2A9-4447-46FB-AB92-D1A845BC24E8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{948F361F-2616-4C96-8D1F-F3CFB1594B55}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21100" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1042" yWindow="1042" windowWidth="26183" windowHeight="14408" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="scRNA Libraries" sheetId="1" r:id="rId1"/>
@@ -1289,7 +1289,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:O53"/>
-  <sheetFormatPr defaultRowHeight="12.5" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="8.73046875" defaultRowHeight="12.75" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="3" width="12" style="2" customWidth="1"/>
     <col min="4" max="5" width="18" style="2" customWidth="1"/>
@@ -1301,10 +1301,10 @@
     <col min="11" max="11" width="22" style="2" customWidth="1"/>
     <col min="12" max="14" width="10" style="2" customWidth="1"/>
     <col min="15" max="15" width="11" style="2" customWidth="1"/>
-    <col min="16" max="16384" width="8.7265625" style="2"/>
+    <col min="16" max="16384" width="8.73046875" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:15" ht="13" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:15" ht="13.15" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1351,7 +1351,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="2" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A2" s="3" t="s">
         <v>15</v>
       </c>
@@ -1398,7 +1398,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A3" s="5" t="s">
         <v>26</v>
       </c>
@@ -1445,7 +1445,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A4" s="3" t="s">
         <v>34</v>
       </c>
@@ -1492,7 +1492,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="5" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A5" s="5" t="s">
         <v>40</v>
       </c>
@@ -1539,7 +1539,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="6" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A6" s="3" t="s">
         <v>45</v>
       </c>
@@ -1586,7 +1586,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="7" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A7" s="5" t="s">
         <v>47</v>
       </c>
@@ -1633,7 +1633,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="8" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A8" s="3" t="s">
         <v>53</v>
       </c>
@@ -1680,7 +1680,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="9" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A9" s="5" t="s">
         <v>56</v>
       </c>
@@ -1727,7 +1727,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="10" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A10" s="3" t="s">
         <v>60</v>
       </c>
@@ -1774,7 +1774,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="11" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A11" s="5" t="s">
         <v>64</v>
       </c>
@@ -1821,7 +1821,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="12" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A12" s="3" t="s">
         <v>67</v>
       </c>
@@ -1868,7 +1868,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="13" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A13" s="5" t="s">
         <v>71</v>
       </c>
@@ -1915,7 +1915,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="14" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A14" s="3" t="s">
         <v>73</v>
       </c>
@@ -1962,7 +1962,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="15" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A15" s="5" t="s">
         <v>76</v>
       </c>
@@ -2009,7 +2009,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="16" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A16" s="3" t="s">
         <v>79</v>
       </c>
@@ -2054,7 +2054,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="17" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A17" s="5" t="s">
         <v>86</v>
       </c>
@@ -2099,7 +2099,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="18" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A18" s="3" t="s">
         <v>91</v>
       </c>
@@ -2144,7 +2144,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="19" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A19" s="5" t="s">
         <v>96</v>
       </c>
@@ -2189,7 +2189,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="20" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A20" s="3" t="s">
         <v>99</v>
       </c>
@@ -2236,7 +2236,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="21" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A21" s="5" t="s">
         <v>106</v>
       </c>
@@ -2283,7 +2283,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="22" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A22" s="3" t="s">
         <v>111</v>
       </c>
@@ -2330,7 +2330,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="23" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A23" s="5" t="s">
         <v>117</v>
       </c>
@@ -2377,7 +2377,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="24" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A24" s="3" t="s">
         <v>122</v>
       </c>
@@ -2424,7 +2424,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="25" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A25" s="5" t="s">
         <v>125</v>
       </c>
@@ -2471,7 +2471,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="26" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A26" s="3" t="s">
         <v>128</v>
       </c>
@@ -2518,7 +2518,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="27" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A27" s="5" t="s">
         <v>130</v>
       </c>
@@ -2565,7 +2565,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="28" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A28" s="3" t="s">
         <v>134</v>
       </c>
@@ -2612,7 +2612,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="29" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A29" s="5" t="s">
         <v>142</v>
       </c>
@@ -2657,7 +2657,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="30" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A30" s="3" t="s">
         <v>147</v>
       </c>
@@ -2704,7 +2704,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="31" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A31" s="5" t="s">
         <v>153</v>
       </c>
@@ -2749,7 +2749,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="32" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A32" s="3" t="s">
         <v>158</v>
       </c>
@@ -2794,7 +2794,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="33" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A33" s="5" t="s">
         <v>164</v>
       </c>
@@ -2841,7 +2841,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="34" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A34" s="3" t="s">
         <v>171</v>
       </c>
@@ -2886,7 +2886,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="35" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A35" s="5" t="s">
         <v>176</v>
       </c>
@@ -2931,7 +2931,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="36" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A36" s="3" t="s">
         <v>182</v>
       </c>
@@ -2976,7 +2976,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="37" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A37" s="5" t="s">
         <v>188</v>
       </c>
@@ -3021,7 +3021,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="38" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A38" s="3" t="s">
         <v>195</v>
       </c>
@@ -3068,7 +3068,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="39" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A39" s="5" t="s">
         <v>203</v>
       </c>
@@ -3113,7 +3113,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="40" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A40" s="3" t="s">
         <v>208</v>
       </c>
@@ -3158,7 +3158,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="41" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A41" s="5" t="s">
         <v>214</v>
       </c>
@@ -3205,7 +3205,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="42" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A42" s="3" t="s">
         <v>221</v>
       </c>
@@ -3250,7 +3250,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="43" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A43" s="5" t="s">
         <v>226</v>
       </c>
@@ -3297,7 +3297,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="44" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A44" s="3" t="s">
         <v>232</v>
       </c>
@@ -3342,7 +3342,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="45" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A45" s="5" t="s">
         <v>237</v>
       </c>
@@ -3387,7 +3387,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="46" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A46" s="3" t="s">
         <v>243</v>
       </c>
@@ -3432,7 +3432,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="47" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A47" s="5" t="s">
         <v>248</v>
       </c>
@@ -3479,7 +3479,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="48" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A48" s="3" t="s">
         <v>255</v>
       </c>
@@ -3524,7 +3524,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="49" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A49" s="5" t="s">
         <v>260</v>
       </c>
@@ -3569,7 +3569,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="50" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A50" s="3" t="s">
         <v>265</v>
       </c>
@@ -3614,7 +3614,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="51" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A51" s="5" t="s">
         <v>271</v>
       </c>
@@ -3659,7 +3659,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="52" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A52" s="3" t="s">
         <v>276</v>
       </c>
@@ -3704,7 +3704,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="53" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A53" s="5" t="s">
         <v>282</v>
       </c>
